--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>81135580</v>
       </c>
       <c r="B13" t="n">
-        <v>58057</v>
+        <v>58110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>81135580</v>
       </c>
       <c r="B13" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>81135580</v>
       </c>
       <c r="B13" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 20365-2022 artfynd.xlsx
+++ b/artfynd/A 20365-2022 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>81135580</v>
       </c>
       <c r="B13" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
